--- a/output/xgb_clf/01_feature_analysis/特征分析报告.xlsx
+++ b/output/xgb_clf/01_feature_analysis/特征分析报告.xlsx
@@ -11,7 +11,6 @@
     <sheet name="by_dataset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="by_month" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="特征分箱图" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="特征分箱图1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,7 +148,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -169,12 +168,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -194,12 +193,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -221,10 +220,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -244,12 +243,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -269,12 +268,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -296,10 +295,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -319,12 +318,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -344,12 +343,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -371,10 +370,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -394,12 +393,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -419,12 +418,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -446,10 +445,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -469,12 +468,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -494,12 +493,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -30330,57 +30329,50 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="68.57142857142857" customWidth="1" min="2" max="2"/>
+    <col width="68.57142857142857" customWidth="1" min="3" max="3"/>
+    <col width="68.57142857142857" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="426.6666666666667" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="23" ht="426.6666666666667" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>f2</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="45" ht="426.6666666666667" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>f3</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="67" ht="426.6666666666667" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>f4</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="89" ht="426.6666666666667" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>f5</t>
         </is>
